--- a/BOM/PICO器件购买清单1014_杨宸涵.xlsx
+++ b/BOM/PICO器件购买清单1014_杨宸涵.xlsx
@@ -64,7 +64,7 @@
     <t>灵足时代关节电机模组ROBSTRIDE00（含CAN调试）</t>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?from=cart&amp;id=1079314226848&amp;mi_id=0000QWWUmhJdZNyrhWbHIbM_y8wxuX-DpCGxr3dVRSjLCbQ&amp;skuId=6132962189472&amp;spm=a1z0d.6639537%2F202410.item.d1079314226848.69167484p4AFV7&amp;upStreamPrice=89900&amp;xxc=taobaoSearch</t>
+    <t>https://item.taobao.com/item.htm?abbucket=0&amp;id=854268859209&amp;mi_id=0000qhuKzSVv0EOtI3Vy_XNeN4kY43dLXlAKqEFG5dtcMV8&amp;ns=1&amp;skuId=5823819118764&amp;spm=a21xtw.29978516.product_shelf.3.2ba71cb7MmqAMo&amp;xxc=taobaoSearch</t>
   </si>
   <si>
     <t>灵足时代 多功能电源管理模块</t>
@@ -768,7 +768,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -794,9 +794,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1415,18 +1412,18 @@
       <c r="E3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="3">
         <v>399</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>1</v>
       </c>
       <c r="D4" s="3">
@@ -1436,30 +1433,30 @@
       <c r="E4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6">
-      <c r="A5" s="10"/>
+      <c r="A5" s="9"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="11"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="3"/>
       <c r="E5" s="5"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6">
-      <c r="A6" s="10"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="11"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="3"/>
       <c r="E6" s="5"/>
       <c r="F6" s="6"/>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6">
       <c r="A7" s="7"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="3"/>
       <c r="E7" s="5"/>
       <c r="F7" s="6"/>
@@ -1481,17 +1478,17 @@
       <c r="F9" s="6"/>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <f>SUM(D2:D8)</f>
         <v>1936</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1499,8 +1496,8 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="https://item.taobao.com/item.htm?from=cart&amp;id=1079314226848&amp;mi_id=0000QWWUmhJdZNyrhWbHIbM_y8wxuX-DpCGxr3dVRSjLCbQ&amp;skuId=6299088163686&amp;spm=a1z0d.6639537%2F202410.item.d1079314226848.69167484p4AFV7&amp;upStreamPrice=89900&amp;xxc=taobaoSearch"/>
-    <hyperlink ref="F3" r:id="rId2" display="https://item.taobao.com/item.htm?from=cart&amp;id=1079314226848&amp;mi_id=0000QWWUmhJdZNyrhWbHIbM_y8wxuX-DpCGxr3dVRSjLCbQ&amp;skuId=6132962189472&amp;spm=a1z0d.6639537%2F202410.item.d1079314226848.69167484p4AFV7&amp;upStreamPrice=89900&amp;xxc=taobaoSearch"/>
-    <hyperlink ref="F4" r:id="rId3" display="https://item.taobao.com/item.htm?abbucket=0&amp;id=1025248375262&amp;mi_id=000048G5xOaak49ofo42Fry-inHjaAv6_2u7zB50EbCiXhg&amp;ns=1&amp;skuId=6202661899589&amp;spm=a21xtw.29978516.product_shelf.10.2ba71cb7MmqAMo&amp;xxc=taobaoSearch"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://item.taobao.com/item.htm?abbucket=0&amp;id=1025248375262&amp;mi_id=000048G5xOaak49ofo42Fry-inHjaAv6_2u7zB50EbCiXhg&amp;ns=1&amp;skuId=6202661899589&amp;spm=a21xtw.29978516.product_shelf.10.2ba71cb7MmqAMo&amp;xxc=taobaoSearch"/>
+    <hyperlink ref="F3" r:id="rId3" display="https://item.taobao.com/item.htm?abbucket=0&amp;id=854268859209&amp;mi_id=0000qhuKzSVv0EOtI3Vy_XNeN4kY43dLXlAKqEFG5dtcMV8&amp;ns=1&amp;skuId=5823819118764&amp;spm=a21xtw.29978516.product_shelf.3.2ba71cb7MmqAMo&amp;xxc=taobaoSearch"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
